--- a/Constraining Model.xlsx
+++ b/Constraining Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ZachF\Desktop\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BD8FC1-199B-4071-9AB0-4D352C636085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D4FC98-A5E2-4123-9927-9E4C184FE0EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F1071FBE-1481-40C0-A7DD-189F6F27206A}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{F1071FBE-1481-40C0-A7DD-189F6F27206A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -106,12 +106,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -126,11 +132,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,7 +500,7 @@
       <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="V1" t="s">
@@ -520,7 +527,7 @@
       <c r="F2" t="s">
         <v>9</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>1000</v>
       </c>
       <c r="V2">
@@ -549,7 +556,7 @@
       <c r="F3" t="s">
         <v>8</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>1200</v>
       </c>
       <c r="V3">
@@ -671,12 +678,12 @@
         <v/>
       </c>
       <c r="I8" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="I8:L12" ca="1">_xlfn.IFNA(_xlfn.VSTACK(_xlfn.HSTACK("","MetricA"),_xlfn.PIVOTBY(_xlfn.VSTACK(A1,_xlfn.ANCHORARRAY(A2)),D1:D35,B1:B35,_xleta.SUM)),"")</f>
+        <f t="array" aca="1" ref="I8:L12" ca="1">_xlfn.IFNA(_xlfn.VSTACK(_xlfn.HSTACK("","ConstA"),_xlfn.PIVOTBY(_xlfn.VSTACK(A1,_xlfn.ANCHORARRAY(A2)),D1:D35,B1:B35,_xleta.SUM)),"")</f>
         <v/>
       </c>
       <c r="J8" s="1" t="str">
         <f ca="1"/>
-        <v>MetricA</v>
+        <v>ConstA</v>
       </c>
       <c r="K8" s="1" t="str">
         <f ca="1"/>
